--- a/experiments/results/resnet34/CIFAR-10/DICE/adaptive/std/results.xlsx
+++ b/experiments/results/resnet34/CIFAR-10/DICE/adaptive/std/results.xlsx
@@ -353,7 +353,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col width="61.33203125" customWidth="1" style="3" min="15" max="15"/>
@@ -862,6 +862,104 @@
       <c r="O10" s="5" t="inlineStr">
         <is>
           <t>dice_p=85,ash_p=None,react_th=None,scale_th=1.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>98.26000000000001</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>35.83</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>92.56999999999999</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>98.63</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>20.18</v>
+      </c>
+      <c r="H11" s="5" t="n">
+        <v>96.43000000000001</v>
+      </c>
+      <c r="I11" s="5" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>99.90000000000001</v>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>13.27</v>
+      </c>
+      <c r="N11" s="5" t="n">
+        <v>97.40000000000001</v>
+      </c>
+      <c r="O11" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=50,ash_p=None,react_th=None,scale_th=1.0,type=std</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>7.61</v>
+      </c>
+      <c r="B12" s="5" t="n">
+        <v>98.59</v>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>36.77</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>92.47</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>6.59</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>17.18</v>
+      </c>
+      <c r="H12" s="5" t="n">
+        <v>97.15000000000001</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="J12" s="5" t="n">
+        <v>99.93000000000001</v>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>98.67</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="N12" s="5" t="n">
+        <v>97.59</v>
+      </c>
+      <c r="O12" s="5" t="inlineStr">
+        <is>
+          <t>dice_p=85,ash_p=None,react_th=None,scale_th=1.1,type=std</t>
         </is>
       </c>
     </row>
